--- a/dashboard-cancer-chile/Cancer_Chile_BaseDatos.xlsx
+++ b/dashboard-cancer-chile/Cancer_Chile_BaseDatos.xlsx
@@ -13,15 +13,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CervixTasa" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CervixMuertes" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pesquisa" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChileMundo" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SobrevidaEtapa" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SimuladorSupuestos" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TopIncidencia" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TopMortalidad" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PorSexo" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MuertesSerie" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prevencion" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPILargo" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChileMundoLargo" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SobrevidaLargo" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChileMundo" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SobrevidaEtapa" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SimuladorSupuestos" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TopIncidencia" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TopMortalidad" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PorSexo" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MuertesSerie" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prevencion" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -69,9 +73,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -166,7 +176,68 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="TopIncidencia" displayName="TopIncidencia" ref="A1:E6" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Fuentes" displayName="Fuentes" ref="A1:C16" headerRowCount="1">
+  <autoFilter ref="A1:C10"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="FuenteID"/>
+    <tableColumn id="2" name="Referencia"/>
+    <tableColumn id="3" name="URL"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="ChileMundo" displayName="ChileMundo" ref="A1:O7" headerRowCount="1">
+  <autoFilter ref="A1:O7"/>
+  <tableColumns count="15">
+    <tableColumn id="1" name="Cancer"/>
+    <tableColumn id="2" name="Chile_TasaIncidencia"/>
+    <tableColumn id="3" name="Chile_TasaMortalidad"/>
+    <tableColumn id="4" name="Mundo_TasaIncidencia"/>
+    <tableColumn id="5" name="Mundo_TasaMortalidad"/>
+    <tableColumn id="6" name="Chile_Casos"/>
+    <tableColumn id="7" name="Chile_Muertes"/>
+    <tableColumn id="8" name="LatAm_Casos"/>
+    <tableColumn id="9" name="LatAm_Muertes"/>
+    <tableColumn id="10" name="Mundo_Casos"/>
+    <tableColumn id="11" name="Mundo_Muertes"/>
+    <tableColumn id="12" name="Chile_MuertesPor10"/>
+    <tableColumn id="13" name="LatAm_MuertesPor10"/>
+    <tableColumn id="14" name="Mundo_MuertesPor10"/>
+    <tableColumn id="15" name="FuenteID"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="SobrevidaEtapa" displayName="SobrevidaEtapa" ref="A1:D7" headerRowCount="1">
+  <autoFilter ref="A1:D7"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Cancer"/>
+    <tableColumn id="2" name="SobrevidaLocalizado"/>
+    <tableColumn id="3" name="SobrevidaMetastasis"/>
+    <tableColumn id="4" name="FuenteID"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="SimuladorSupuestos" displayName="SimuladorSupuestos" ref="A1:C6" headerRowCount="1">
+  <autoFilter ref="A1:C6"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Supuesto"/>
+    <tableColumn id="2" name="Valor"/>
+    <tableColumn id="3" name="FuenteID"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="TopIncidencia" displayName="TopIncidencia" ref="A1:E6" headerRowCount="1">
   <autoFilter ref="A1:E6"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Orden"/>
@@ -179,8 +250,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="TopMortalidad" displayName="TopMortalidad" ref="A1:D5" headerRowCount="1">
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="TopMortalidad" displayName="TopMortalidad" ref="A1:D5" headerRowCount="1">
   <autoFilter ref="A1:D5"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Orden"/>
@@ -192,8 +263,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="PorSexo" displayName="PorSexo" ref="A1:E7" headerRowCount="1">
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="PorSexo" displayName="PorSexo" ref="A1:E7" headerRowCount="1">
   <autoFilter ref="A1:E7"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Sexo"/>
@@ -206,8 +277,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="MuertesSerie" displayName="MuertesSerie" ref="A1:E8" headerRowCount="1">
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="MuertesSerie" displayName="MuertesSerie" ref="A1:E8" headerRowCount="1">
   <autoFilter ref="A1:E8"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Anio"/>
@@ -220,8 +291,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Prevencion" displayName="Prevencion" ref="A1:E8" headerRowCount="1">
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="Prevencion" displayName="Prevencion" ref="A1:E8" headerRowCount="1">
   <autoFilter ref="A1:E8"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Orden"/>
@@ -288,63 +359,59 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Fuentes" displayName="Fuentes" ref="A1:C16" headerRowCount="1">
-  <autoFilter ref="A1:C10"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="FuenteID"/>
-    <tableColumn id="2" name="Referencia"/>
-    <tableColumn id="3" name="URL"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="KPI" displayName="KPI" ref="A1:I12" headerRowCount="1">
+  <autoFilter ref="A1:I12"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="Orden"/>
+    <tableColumn id="2" name="Area"/>
+    <tableColumn id="3" name="KPI"/>
+    <tableColumn id="4" name="Valor"/>
+    <tableColumn id="5" name="Formula"/>
+    <tableColumn id="6" name="QueMide"/>
+    <tableColumn id="7" name="PorQue"/>
+    <tableColumn id="8" name="Meta"/>
+    <tableColumn id="9" name="FuenteID"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="ChileMundo" displayName="ChileMundo" ref="A1:O7" headerRowCount="1">
-  <autoFilter ref="A1:O7"/>
-  <tableColumns count="15">
-    <tableColumn id="1" name="Cancer"/>
-    <tableColumn id="2" name="Chile_TasaIncidencia"/>
-    <tableColumn id="3" name="Chile_TasaMortalidad"/>
-    <tableColumn id="4" name="Mundo_TasaIncidencia"/>
-    <tableColumn id="5" name="Mundo_TasaMortalidad"/>
-    <tableColumn id="6" name="Chile_Casos"/>
-    <tableColumn id="7" name="Chile_Muertes"/>
-    <tableColumn id="8" name="LatAm_Casos"/>
-    <tableColumn id="9" name="LatAm_Muertes"/>
-    <tableColumn id="10" name="Mundo_Casos"/>
-    <tableColumn id="11" name="Mundo_Muertes"/>
-    <tableColumn id="12" name="Chile_MuertesPor10"/>
-    <tableColumn id="13" name="LatAm_MuertesPor10"/>
-    <tableColumn id="14" name="Mundo_MuertesPor10"/>
-    <tableColumn id="15" name="FuenteID"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="KPILargo" displayName="KPILargo" ref="A1:E78" headerRowCount="1">
+  <autoFilter ref="A1:E78"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="OrdenKPI"/>
+    <tableColumn id="2" name="KPI"/>
+    <tableColumn id="3" name="OrdenCampo"/>
+    <tableColumn id="4" name="Campo"/>
+    <tableColumn id="5" name="Valor"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="SobrevidaEtapa" displayName="SobrevidaEtapa" ref="A1:D7" headerRowCount="1">
-  <autoFilter ref="A1:D7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="ChileMundoLargo" displayName="ChileMundoLargo" ref="A1:D43" headerRowCount="1">
+  <autoFilter ref="A1:D43"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Cancer"/>
-    <tableColumn id="2" name="SobrevidaLocalizado"/>
-    <tableColumn id="3" name="SobrevidaMetastasis"/>
-    <tableColumn id="4" name="FuenteID"/>
+    <tableColumn id="2" name="Indicador"/>
+    <tableColumn id="3" name="Lugar"/>
+    <tableColumn id="4" name="Valor"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="SimuladorSupuestos" displayName="SimuladorSupuestos" ref="A1:C6" headerRowCount="1">
-  <autoFilter ref="A1:C6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="SobrevidaLargo" displayName="SobrevidaLargo" ref="A1:C13" headerRowCount="1">
+  <autoFilter ref="A1:C13"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Supuesto"/>
-    <tableColumn id="2" name="Valor"/>
-    <tableColumn id="3" name="FuenteID"/>
+    <tableColumn id="1" name="Cancer"/>
+    <tableColumn id="2" name="Etapa"/>
+    <tableColumn id="3" name="Sobrevida"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -668,114 +735,209 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Supuesto</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>FuenteID</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Cancer</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Etapa</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Sobrevida</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Reducción de mortalidad por mamografía en mujeres 50-69 que se la hacen</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>C11</t>
-        </is>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Localizado</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>99</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Fracción de muertes por cáncer de mama en 50-69 años (supuesto)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Supuesto propio</t>
-        </is>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Cuello uterino</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Localizado</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>91</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cobertura actual de mamografía 50-69</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>37,4%</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>C5</t>
-        </is>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Endometrio</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Localizado</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Reducción de casos de cáncer cervicouterino con tamizaje cada 3-5 años</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>C11</t>
-        </is>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Ovario</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Localizado</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>93</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Cobertura actual estimada de PAP</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>43%</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Testículo</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Localizado</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Próstata</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Localizado</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Con metástasis</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Cuello uterino</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Con metástasis</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Endometrio</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Con metástasis</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Ovario</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Con metástasis</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Testículo</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Con metástasis</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Próstata</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Con metástasis</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -792,138 +954,283 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Orden</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Cancer</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>CasosNuevos</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>PorcentajeCasos</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>FuenteID</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Referencia</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Próstata</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>8758</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="E2" t="inlineStr">
+          <t>GLOBOCAN 2024 (IARC/OMS, sept. 2026): Chile, Latinoamérica y el Caribe, Mundo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://gco.iarc.who.int/media/globocan/factsheets/populations/152-chile-fact-sheet.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MINSAL: reducción 56% mortalidad cáncer cervicouterino (2025)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.minsal.cl/ministra-aguilera-destaca-reduccion-del-56-en-mortalidad-por-cancer-cervicouterino-gracias-a-politicas-de-estado/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BCN 2023: Cáncer de mama y mamografías en Chile</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://obtienearchivo.bcn.cl/obtienearchivo?id=repositorio/10221/34431/1/202307_BCN_Cancer_de_mama_y_mamografias.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DEIS vía 24horas (16-10-2024)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.24horas.cl/tendencias/tecnologia-y-ciencias/muertes-por-cancer-de-mama-aumentan-un-12-87-en-chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Observatorio del Cáncer vía La Tercera (21-10-2025)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.latercera.com/nacional/noticia/observatorio-del-cancer-revela-cifras-decidoras-solo-4-de-cada-10-mujeres-de-50-a-69-anos-tienen-su-mamografia-al-dia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DEIS vía Vergara 240 UDP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://vergara240.udp.cl/chile-790-muertes-anuales-cancer-cervicouterino/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MINSAL Guía GES Cáncer de testículo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://diprece.minsal.cl/le-informamos/auge/acceso-guias-clinicas/guias-clinicas-desarrolladas-utilizando-manual-metodologico/cancer-de-testiculos-en-personas-de-15-anos-y-mas/descripcion-y-epidemiologia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>IARC Handbooks vol. 15 (2016) y vol. 10 (2005): tamizaje de mama y cervicouterino</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://publications.iarc.who.int/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>American Cancer Society / SEER: sobrevida a 5 años por etapa</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.cancer.org/research/cancer-facts-statistics.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>C13</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Colorrectal</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>7965</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>C13</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Estómago</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>5494</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>C13</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Mama</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>5141</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>C13</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Pulmón</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>4368</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>C13</t>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GLOBOCAN 2024 vía Observatorio del Cáncer: Radiografía del cáncer en Chile</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.observatoriodelcancer.cl/post/radiograf%C3%ADa-del-c%C3%A1ncer-en-chile-qu%C3%A9-revelan-las-cifras-de-globocan-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>INE Estadísticas Vitales 2019 vía La Tercera: el cáncer es por primera vez la principal causa de muerte</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.latercera.com/la-tercera-sabado/noticia/cancer-es-por-primera-vez-la-principal-causa-de-muerte-en-chile/KIPWS6M5HNHMJCE27GVGYJS52U/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>C15</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>INE: 25,9% de las muertes en 2017 se produjo por tumores</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.ine.gob.cl/sala-de-prensa/prensa/general/noticia/2020/02/04/c%C3%A1ncer-en-chile-25-9-de-las-muertes-en-2017-se-produjo-por-tumores</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DEIS-MINSAL vía El Mercurio y GesNova Salud: defunciones por tumores 2023 y 2024 (preliminar)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://gesnovasalud.com/en-2024-se-agudizo-el-alza-de-muertes-por-cancer-y-patologias-del-sistema-circulatorio/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>OMS/IARC, Nature Medicine 2026: 37,8% de los cánceres se asocia a factores de riesgo modificables</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.24horas.cl/conciencia-24-7/ciencia/oms-cuatro-diez-canceres-podrian-prevenirse</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>C18</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>IARC (GLOBOCAN 2018) vía AFP/24horas: proyección de casos y muertes en Chile a 2040</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.24horas.cl/tendencias/salud-bienestar/las-preocupantes-cifras-del-aumento-de-cancer-en-chile-3048324</t>
         </is>
       </c>
     </row>
@@ -941,98 +1248,404 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Orden</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cancer</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Muertes</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Chile_TasaIncidencia</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Chile_TasaMortalidad</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Mundo_TasaIncidencia</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Mundo_TasaMortalidad</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Chile_Casos</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Chile_Muertes</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LatAm_Casos</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LatAm_Muertes</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Mundo_Casos</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Mundo_Muertes</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Chile_MuertesPor10</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LatAm_MuertesPor10</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Mundo_MuertesPor10</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>FuenteID</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Pulmón</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>29.4</v>
       </c>
       <c r="C2" t="n">
-        <v>3965</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>C13</t>
+        <v>10.1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5141</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1829</v>
+      </c>
+      <c r="H2" t="n">
+        <v>218121</v>
+      </c>
+      <c r="I2" t="n">
+        <v>61565</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2434087</v>
+      </c>
+      <c r="K2" t="n">
+        <v>693660</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>C1</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cuello uterino</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1905</v>
+      </c>
+      <c r="G3" t="n">
+        <v>843</v>
+      </c>
+      <c r="H3" t="n">
+        <v>66200</v>
+      </c>
+      <c r="I3" t="n">
+        <v>33068</v>
+      </c>
+      <c r="J3" t="n">
+        <v>604196</v>
+      </c>
+      <c r="K3" t="n">
+        <v>279583</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Endometrio</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Colorrectal</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>3794</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>C13</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="D4" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1076</v>
+      </c>
+      <c r="G4" t="n">
+        <v>398</v>
+      </c>
+      <c r="H4" t="n">
+        <v>38342</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9252</v>
+      </c>
+      <c r="J4" t="n">
+        <v>434620</v>
+      </c>
+      <c r="K4" t="n">
+        <v>100680</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ovario</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>838</v>
+      </c>
+      <c r="G5" t="n">
+        <v>600</v>
+      </c>
+      <c r="H5" t="n">
+        <v>26914</v>
+      </c>
+      <c r="I5" t="n">
+        <v>15684</v>
+      </c>
+      <c r="J5" t="n">
+        <v>330731</v>
+      </c>
+      <c r="K5" t="n">
+        <v>203850</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Testículo</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>774</v>
+      </c>
+      <c r="G6" t="n">
+        <v>113</v>
+      </c>
+      <c r="H6" t="n">
+        <v>11822</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2181</v>
+      </c>
+      <c r="J6" t="n">
+        <v>70714</v>
+      </c>
+      <c r="K6" t="n">
+        <v>9240</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Próstata</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8758</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2605</v>
+      </c>
+      <c r="H7" t="n">
+        <v>215448</v>
+      </c>
+      <c r="I7" t="n">
+        <v>63058</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1546112</v>
+      </c>
+      <c r="K7" t="n">
+        <v>419849</v>
+      </c>
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Estómago</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>3511</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>C13</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Mama</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1829</v>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="M7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
@@ -1052,31 +1665,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Sexo</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Orden</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cancer</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>PorcentajeCasos</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>SobrevidaLocalizado</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>SobrevidaMetastasis</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>FuenteID</t>
         </is>
@@ -1085,138 +1699,108 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hombres</t>
+          <t>Mama</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Próstata</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>C13</t>
+        <v>99</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>C12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hombres</t>
+          <t>Cuello uterino</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Colorrectal</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>C13</t>
+        <v>91</v>
+      </c>
+      <c r="C3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>C12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hombres</t>
+          <t>Endometrio</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Estómago</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>C13</t>
+        <v>95</v>
+      </c>
+      <c r="C4" t="n">
+        <v>18</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>C12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mujeres</t>
+          <t>Ovario</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Mama</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>C13</t>
+        <v>93</v>
+      </c>
+      <c r="C5" t="n">
+        <v>31</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>C12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mujeres</t>
+          <t>Testículo</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Colorrectal</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>C13</t>
+        <v>99</v>
+      </c>
+      <c r="C6" t="n">
+        <v>73</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>C12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mujeres</t>
+          <t>Próstata</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Cuello uterino</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>C13</t>
+        <v>99</v>
+      </c>
+      <c r="C7" t="n">
+        <v>37</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>C12</t>
         </is>
       </c>
     </row>
@@ -1234,174 +1818,113 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Anio</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>MuertesPorCancer</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>PorcentajeDefunciones</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Nota</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Supuesto</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>FuenteID</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B2" t="n">
-        <v>18394</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Tumores malignos</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>C14</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reducción de mortalidad por mamografía en mujeres 50-69 que se la hacen</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>C11</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B3" t="n">
-        <v>26866</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Tumores</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>C15</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Fracción de muertes por cáncer de mama en 50-69 años (supuesto)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Supuesto propio</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B4" t="n">
-        <v>27183</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.261</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Tumores</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>C15</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Cobertura actual de mamografía 50-69</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>37,4%</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C5</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B5" t="n">
-        <v>27504</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Tumores</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>C15</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Reducción de casos de cáncer cervicouterino con tamizaje cada 3-5 años</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C11</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B6" t="n">
-        <v>28492</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Primera causa de muerte por primera vez</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>C14</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B7" t="n">
-        <v>29636</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Tumores</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>C16</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B8" t="n">
-        <v>31454</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Dato preliminar</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>C16</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cobertura actual estimada de PAP</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C6</t>
         </is>
       </c>
     </row>
@@ -1414,6 +1937,633 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Orden</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Cancer</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>CasosNuevos</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PorcentajeCasos</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>FuenteID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Próstata</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>8758</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Colorrectal</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>7965</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Estómago</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5494</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5141</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pulmón</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4368</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Orden</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Cancer</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Muertes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FuenteID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pulmón</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3965</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Colorrectal</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3794</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Estómago</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3511</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1829</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Sexo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Orden</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Cancer</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PorcentajeCasos</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>FuenteID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Hombres</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Próstata</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Hombres</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Colorrectal</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Hombres</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Estómago</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Mujeres</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mujeres</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Colorrectal</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mujeres</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Cuello uterino</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Anio</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>MuertesPorCancer</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>PorcentajeDefunciones</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>FuenteID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B2" t="n">
+        <v>18394</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Tumores malignos</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B3" t="n">
+        <v>26866</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Tumores</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>C15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B4" t="n">
+        <v>27183</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Tumores</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>C15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B5" t="n">
+        <v>27504</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Tumores</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>C15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B6" t="n">
+        <v>28492</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Primera causa de muerte por primera vez</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B7" t="n">
+        <v>29636</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Tumores</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B8" t="n">
+        <v>31454</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Dato preliminar</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2385,283 +3535,559 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Orden</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>QueMide</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>PorQue</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>FuenteID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Referencia</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Resumen</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos de cáncer al año</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>59.887 (2024)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Número de casos nuevos estimados en el año</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Carga total de cáncer en Chile</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Sirve para planificar oncólogos, quimioterapia, cirugías y camas</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>¿Está aumentando?</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Variación de muertes por cáncer</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>+71% (2001–2024)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>(Muertes 2024 − muertes 2001) ÷ muertes 2001 × 100</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Cuánto ha aumentado la mortalidad por cáncer</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Se explica en parte por el envejecimiento: por eso importan la prevención y la detección precoz</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>C14;C16</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>¿Está aumentando?</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Proporción de muertes por cáncer</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>1 de cada 4 muertes (26%)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por cáncer ÷ total de defunciones × 100</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Peso del cáncer entre todas las causas de muerte</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Desde 2019 es la primera causa de muerte en Chile</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>C14;C15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Chile y el mundo</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia por 100 mil</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Mama: 29,4</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos ÷ población × 100.000</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Riesgo de que aparezca un cáncer en un año</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Permite comparar Chile con el mundo y entre tipos de cáncer</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Mundo, mama: 47,8</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>GLOBOCAN 2024 (IARC/OMS, sept. 2026): Chile, Latinoamérica y el Caribe, Mundo</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://gco.iarc.who.int/media/globocan/factsheets/populations/152-chile-fact-sheet.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Chile y el mundo</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad por 100 mil</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Mama: 10,1</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Muertes ÷ población × 100.000</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Riesgo de morir por ese cáncer en un año</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Junto a la incidencia muestra cuán letal es cada cáncer</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Mundo, mama: 12,9</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Chile y el mundo</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Razón mortalidad / incidencia</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Mama: 3,6 muertes por cada 10 casos</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Muertes ÷ casos nuevos × 10</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Cuántos mueren por cada 10 diagnosticados</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Es un reflejo del acceso a diagnóstico precoz y tratamiento: más bajo es mejor</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Mundo, mama: 2,8</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Cáncer de mama</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de mamografía vigente</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>37,4% (mujeres de 50 a 69)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Mujeres con mamografía al día ÷ mujeres de 50 a 69 × 100</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Qué parte de la población objetivo está tamizada</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>La mamografía cada 2 a 3 años reduce cerca de 40% las muertes en quienes se la hacen</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>C5;C11</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Cuello uterino</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de PAP vigente</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>43% (estimada)</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Mujeres con PAP al día ÷ mujeres de 25 a 64 × 100</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Qué parte de la población objetivo está tamizada</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>El tamizaje cada 3 a 5 años reduce hasta 80% los casos de cáncer cervicouterino</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>OMS 2030: 70% tamizadas con test de alta calidad</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>C6;C11</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Cuello uterino</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de vacuna VPH</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>86,2% (niñas menores de 15)</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Niñas vacunadas ÷ niñas de la cohorte × 100</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Protección contra el virus que causa el cáncer cervicouterino</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Es la prevención primaria más eficaz; parte de la estrategia de eliminación de la OMS</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>90% (OMS 90-70-90)</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MINSAL: reducción 56% mortalidad cáncer cervicouterino (2025)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.minsal.cl/ministra-aguilera-destaca-reduccion-del-56-en-mortalidad-por-cancer-cervicouterino-gracias-a-politicas-de-estado/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BCN 2023: Cáncer de mama y mamografías en Chile</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://obtienearchivo.bcn.cl/obtienearchivo?id=repositorio/10221/34431/1/202307_BCN_Cancer_de_mama_y_mamografias.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>DEIS vía 24horas (16-10-2024)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.24horas.cl/tendencias/tecnologia-y-ciencias/muertes-por-cancer-de-mama-aumentan-un-12-87-en-chile</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Observatorio del Cáncer vía La Tercera (21-10-2025)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.latercera.com/nacional/noticia/observatorio-del-cancer-revela-cifras-decidoras-solo-4-de-cada-10-mujeres-de-50-a-69-anos-tienen-su-mamografia-al-dia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>DEIS vía Vergara 240 UDP</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://vergara240.udp.cl/chile-790-muertes-anuales-cancer-cervicouterino/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>C7</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MINSAL Guía GES Cáncer de testículo</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://diprece.minsal.cl/le-informamos/auge/acceso-guias-clinicas/guias-clinicas-desarrolladas-utilizando-manual-metodologico/cancer-de-testiculos-en-personas-de-15-anos-y-mas/descripcion-y-epidemiologia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>C11</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>IARC Handbooks vol. 15 (2016) y vol. 10 (2005): tamizaje de mama y cervicouterino</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://publications.iarc.who.int/</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Detectarlo a tiempo</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Sobrevida a 5 años según etapa</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Mama: 99% localizado · 32% con metástasis</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Personas vivas a 5 años del diagnóstico ÷ personas diagnosticadas × 100</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Probabilidad de seguir con vida 5 años después</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Muestra el valor de detectar a tiempo: la etapa cambia todo</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>American Cancer Society / SEER: sobrevida a 5 años por etapa</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.cancer.org/research/cancer-facts-statistics.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>C13</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>GLOBOCAN 2024 vía Observatorio del Cáncer: Radiografía del cáncer en Chile</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://www.observatoriodelcancer.cl/post/radiograf%C3%ADa-del-c%C3%A1ncer-en-chile-qu%C3%A9-revelan-las-cifras-de-globocan-2024</t>
-        </is>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>C14</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>INE Estadísticas Vitales 2019 vía La Tercera: el cáncer es por primera vez la principal causa de muerte</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://www.latercera.com/la-tercera-sabado/noticia/cancer-es-por-primera-vez-la-principal-causa-de-muerte-en-chile/KIPWS6M5HNHMJCE27GVGYJS52U/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>C15</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>INE: 25,9% de las muertes en 2017 se produjo por tumores</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>https://www.ine.gob.cl/sala-de-prensa/prensa/general/noticia/2020/02/04/c%C3%A1ncer-en-chile-25-9-de-las-muertes-en-2017-se-produjo-por-tumores</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>C16</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>DEIS-MINSAL vía El Mercurio y GesNova Salud: defunciones por tumores 2023 y 2024 (preliminar)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://gesnovasalud.com/en-2024-se-agudizo-el-alza-de-muertes-por-cancer-y-patologias-del-sistema-circulatorio/</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Cómo prevenirlo</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Fracción atribuible a factores modificables</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>37,8%</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Casos que se evitarían eliminando los factores de riesgo ÷ casos totales × 100</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Qué parte del cáncer se puede prevenir</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Tabaco, alcohol, sedentarismo, obesidad e infecciones (VPH, hepatitis B, H. pylori) se pueden cambiar</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>C17</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>OMS/IARC, Nature Medicine 2026: 37,8% de los cánceres se asocia a factores de riesgo modificables</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://www.24horas.cl/conciencia-24-7/ciencia/oms-cuatro-diez-canceres-podrian-prevenirse</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>C18</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>IARC (GLOBOCAN 2018) vía AFP/24horas: proyección de casos y muertes en Chile a 2040</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://www.24horas.cl/tendencias/salud-bienestar/las-preocupantes-cifras-del-aumento-de-cancer-en-chile-3048324</t>
         </is>
       </c>
     </row>
@@ -2679,406 +4105,1811 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Cancer</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Chile_TasaIncidencia</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Chile_TasaMortalidad</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Mundo_TasaIncidencia</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Mundo_TasaMortalidad</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Chile_Casos</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Chile_Muertes</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>LatAm_Casos</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LatAm_Muertes</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Mundo_Casos</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Mundo_Muertes</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Chile_MuertesPor10</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>LatAm_MuertesPor10</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Mundo_MuertesPor10</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>FuenteID</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>OrdenKPI</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>OrdenCampo</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Campo</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Mama</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="C2" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5141</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1829</v>
-      </c>
-      <c r="H2" t="n">
-        <v>218121</v>
-      </c>
-      <c r="I2" t="n">
-        <v>61565</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2434087</v>
-      </c>
-      <c r="K2" t="n">
-        <v>693660</v>
-      </c>
-      <c r="L2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos de cáncer al año</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>59.887 (2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos de cáncer al año</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Número de casos nuevos estimados en el año</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos de cáncer al año</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Carga total de cáncer en Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos de cáncer al año</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Sirve para planificar oncólogos, quimioterapia, cirugías y camas</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos de cáncer al año</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos de cáncer al año</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Resumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos de cáncer al año</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Variación de muertes por cáncer</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>+71% (2001–2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Variación de muertes por cáncer</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>(Muertes 2024 − muertes 2001) ÷ muertes 2001 × 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Variación de muertes por cáncer</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Cuánto ha aumentado la mortalidad por cáncer</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Variación de muertes por cáncer</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Se explica en parte por el envejecimiento: por eso importan la prevención y la detección precoz</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Variación de muertes por cáncer</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Variación de muertes por cáncer</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>¿Está aumentando?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Variación de muertes por cáncer</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>C14;C16</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Proporción de muertes por cáncer</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>1 de cada 4 muertes (26%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Proporción de muertes por cáncer</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por cáncer ÷ total de defunciones × 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Proporción de muertes por cáncer</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Peso del cáncer entre todas las causas de muerte</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Proporción de muertes por cáncer</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Desde 2019 es la primera causa de muerte en Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Proporción de muertes por cáncer</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Proporción de muertes por cáncer</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>¿Está aumentando?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Proporción de muertes por cáncer</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>C14;C15</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia por 100 mil</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Mama: 29,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia por 100 mil</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos ÷ población × 100.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia por 100 mil</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Riesgo de que aparezca un cáncer en un año</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia por 100 mil</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Permite comparar Chile con el mundo y entre tipos de cáncer</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia por 100 mil</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Mundo, mama: 47,8</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia por 100 mil</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Chile y el mundo</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de incidencia por 100 mil</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad por 100 mil</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Mama: 10,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad por 100 mil</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Muertes ÷ población × 100.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad por 100 mil</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Riesgo de morir por ese cáncer en un año</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad por 100 mil</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Junto a la incidencia muestra cuán letal es cada cáncer</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad por 100 mil</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Mundo, mama: 12,9</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad por 100 mil</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Chile y el mundo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad por 100 mil</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Razón mortalidad / incidencia</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Mama: 3,6 muertes por cada 10 casos</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Razón mortalidad / incidencia</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Muertes ÷ casos nuevos × 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Razón mortalidad / incidencia</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Cuántos mueren por cada 10 diagnosticados</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Razón mortalidad / incidencia</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Es un reflejo del acceso a diagnóstico precoz y tratamiento: más bajo es mejor</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Razón mortalidad / incidencia</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Mundo, mama: 2,8</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Razón mortalidad / incidencia</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Chile y el mundo</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Razón mortalidad / incidencia</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de mamografía vigente</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>37,4% (mujeres de 50 a 69)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de mamografía vigente</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Mujeres con mamografía al día ÷ mujeres de 50 a 69 × 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de mamografía vigente</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Qué parte de la población objetivo está tamizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de mamografía vigente</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>La mamografía cada 2 a 3 años reduce cerca de 40% las muertes en quienes se la hacen</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de mamografía vigente</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de mamografía vigente</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Cáncer de mama</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de mamografía vigente</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>C5;C11</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de PAP vigente</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>43% (estimada)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de PAP vigente</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Mujeres con PAP al día ÷ mujeres de 25 a 64 × 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de PAP vigente</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Qué parte de la población objetivo está tamizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de PAP vigente</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>El tamizaje cada 3 a 5 años reduce hasta 80% los casos de cáncer cervicouterino</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de PAP vigente</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>OMS 2030: 70% tamizadas con test de alta calidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de PAP vigente</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>Cuello uterino</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="C3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1905</v>
-      </c>
-      <c r="G3" t="n">
-        <v>843</v>
-      </c>
-      <c r="H3" t="n">
-        <v>66200</v>
-      </c>
-      <c r="I3" t="n">
-        <v>33068</v>
-      </c>
-      <c r="J3" t="n">
-        <v>604196</v>
-      </c>
-      <c r="K3" t="n">
-        <v>279583</v>
-      </c>
-      <c r="L3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M3" t="n">
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de PAP vigente</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>C6;C11</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de vacuna VPH</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>86,2% (niñas menores de 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de vacuna VPH</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Niñas vacunadas ÷ niñas de la cohorte × 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de vacuna VPH</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Protección contra el virus que causa el cáncer cervicouterino</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de vacuna VPH</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Es la prevención primaria más eficaz; parte de la estrategia de eliminación de la OMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de vacuna VPH</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="N3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Endometrio</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="C4" t="n">
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>90% (OMS 90-70-90)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de vacuna VPH</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Cuello uterino</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Cobertura de vacuna VPH</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Sobrevida a 5 años según etapa</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Mama: 99% localizado · 32% con metástasis</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Sobrevida a 5 años según etapa</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1076</v>
-      </c>
-      <c r="G4" t="n">
-        <v>398</v>
-      </c>
-      <c r="H4" t="n">
-        <v>38342</v>
-      </c>
-      <c r="I4" t="n">
-        <v>9252</v>
-      </c>
-      <c r="J4" t="n">
-        <v>434620</v>
-      </c>
-      <c r="K4" t="n">
-        <v>100680</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Ovario</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F5" t="n">
-        <v>838</v>
-      </c>
-      <c r="G5" t="n">
-        <v>600</v>
-      </c>
-      <c r="H5" t="n">
-        <v>26914</v>
-      </c>
-      <c r="I5" t="n">
-        <v>15684</v>
-      </c>
-      <c r="J5" t="n">
-        <v>330731</v>
-      </c>
-      <c r="K5" t="n">
-        <v>203850</v>
-      </c>
-      <c r="L5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Testículo</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F6" t="n">
-        <v>774</v>
-      </c>
-      <c r="G6" t="n">
-        <v>113</v>
-      </c>
-      <c r="H6" t="n">
-        <v>11822</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2181</v>
-      </c>
-      <c r="J6" t="n">
-        <v>70714</v>
-      </c>
-      <c r="K6" t="n">
-        <v>9240</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Próstata</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="E7" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>8758</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2605</v>
-      </c>
-      <c r="H7" t="n">
-        <v>215448</v>
-      </c>
-      <c r="I7" t="n">
-        <v>63058</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1546112</v>
-      </c>
-      <c r="K7" t="n">
-        <v>419849</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Personas vivas a 5 años del diagnóstico ÷ personas diagnosticadas × 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Sobrevida a 5 años según etapa</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>C1</t>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Probabilidad de seguir con vida 5 años después</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Sobrevida a 5 años según etapa</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Muestra el valor de detectar a tiempo: la etapa cambia todo</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Sobrevida a 5 años según etapa</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Sobrevida a 5 años según etapa</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Detectarlo a tiempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Sobrevida a 5 años según etapa</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Fracción atribuible a factores modificables</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>37,8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Fracción atribuible a factores modificables</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Casos que se evitarían eliminando los factores de riesgo ÷ casos totales × 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Fracción atribuible a factores modificables</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Qué parte del cáncer se puede prevenir</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Fracción atribuible a factores modificables</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Tabaco, alcohol, sedentarismo, obesidad e infecciones (VPH, hepatitis B, H. pylori) se pueden cambiar</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Fracción atribuible a factores modificables</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Fracción atribuible a factores modificables</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Cómo prevenirlo</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Fracción atribuible a factores modificables</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>C17</t>
         </is>
       </c>
     </row>
@@ -3096,143 +5927,875 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Cancer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>SobrevidaLocalizado</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>SobrevidaMetastasis</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>FuenteID</t>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Lugar</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Mama</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>99</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos por 100 mil</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>29.4</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos por 100 mil</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Mundo</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por 100 mil</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por 100 mil</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Mundo</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por cada 10 casos</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por cada 10 casos</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Latinoamérica</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por cada 10 casos</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Mundo</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Cuello uterino</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>91</v>
-      </c>
-      <c r="C3" t="n">
-        <v>19</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos por 100 mil</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Cuello uterino</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos por 100 mil</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Mundo</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Cuello uterino</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por 100 mil</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Cuello uterino</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por 100 mil</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Mundo</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Cuello uterino</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por cada 10 casos</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Cuello uterino</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por cada 10 casos</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Latinoamérica</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Cuello uterino</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por cada 10 casos</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Mundo</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Endometrio</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>95</v>
-      </c>
-      <c r="C4" t="n">
-        <v>18</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos por 100 mil</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Endometrio</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos por 100 mil</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Mundo</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Endometrio</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por 100 mil</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Endometrio</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por 100 mil</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Mundo</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Endometrio</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por cada 10 casos</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Endometrio</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por cada 10 casos</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Latinoamérica</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Endometrio</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por cada 10 casos</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Mundo</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Ovario</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>93</v>
-      </c>
-      <c r="C5" t="n">
-        <v>31</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos por 100 mil</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Ovario</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos por 100 mil</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Mundo</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Ovario</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por 100 mil</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Ovario</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por 100 mil</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Mundo</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Ovario</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por cada 10 casos</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Ovario</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por cada 10 casos</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Latinoamérica</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Ovario</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por cada 10 casos</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Mundo</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Testículo</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>99</v>
-      </c>
-      <c r="C6" t="n">
-        <v>73</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos por 100 mil</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Testículo</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos por 100 mil</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Mundo</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Testículo</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por 100 mil</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Testículo</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por 100 mil</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Mundo</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Testículo</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por cada 10 casos</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Testículo</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por cada 10 casos</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Latinoamérica</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Testículo</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por cada 10 casos</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Mundo</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Próstata</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>99</v>
-      </c>
-      <c r="C7" t="n">
-        <v>37</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos por 100 mil</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>41.1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Próstata</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Casos nuevos por 100 mil</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Mundo</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Próstata</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por 100 mil</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Próstata</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por 100 mil</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Mundo</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Próstata</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por cada 10 casos</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Próstata</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por cada 10 casos</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Latinoamérica</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Próstata</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Muertes por cada 10 casos</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Mundo</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>
